--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
@@ -4839,7 +4839,7 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>34.50717572063278</v>
+        <v>34.50717572063277</v>
       </c>
       <c r="C264">
         <v>26.88315954405832</v>
@@ -4941,7 +4941,7 @@
         <v>269</v>
       </c>
       <c r="B270">
-        <v>60.8283064457127</v>
+        <v>60.82830644571268</v>
       </c>
       <c r="C270">
         <v>78.37118298240142</v>
